--- a/Research Setup/Peta_Posisi_Penelitian.xlsx
+++ b/Research Setup/Peta_Posisi_Penelitian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Habbi Widagdo\Documents\Tugas Akhir\Proposal TA\Research Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5A26F4-0B29-4FCE-A9C2-D8476D551ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC321285-4D44-4FC6-8FF6-E95B6F359BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="52">
   <si>
     <t>Aspek / Fitur Metodologis &amp; Konteks</t>
   </si>
@@ -220,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +272,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -431,7 +438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -514,6 +521,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,10 +877,10 @@
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="16" t="s">
@@ -873,7 +892,7 @@
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="31" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -1028,7 +1047,7 @@
       <c r="F5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="13" t="s">
         <v>21</v>
       </c>
@@ -1051,7 +1070,7 @@
         <v>21</v>
       </c>
       <c r="O5" s="7"/>
-      <c r="P5" s="8"/>
+      <c r="P5" s="30"/>
       <c r="Q5" s="13" t="s">
         <v>21</v>
       </c>
@@ -1064,9 +1083,7 @@
       <c r="T5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="U5" s="5"/>
     </row>
     <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -1093,7 +1110,7 @@
       <c r="J6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="30"/>
       <c r="L6" s="4" t="s">
         <v>21</v>
       </c>
@@ -1106,7 +1123,7 @@
       <c r="O6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="8"/>
+      <c r="P6" s="30"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="22" t="s">
         <v>21</v>
@@ -1146,7 +1163,7 @@
         <v>21</v>
       </c>
       <c r="J7" s="14"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="29"/>
       <c r="L7" s="6" t="s">
         <v>21</v>
       </c>
@@ -1161,7 +1178,7 @@
         <v>21</v>
       </c>
       <c r="Q7" s="14"/>
-      <c r="R7" s="7"/>
+      <c r="R7" s="29"/>
       <c r="S7" s="6" t="s">
         <v>21</v>
       </c>
@@ -1247,14 +1264,14 @@
       <c r="F10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="14"/>
       <c r="I10" s="7"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="7"/>
+      <c r="K10" s="29"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="N10" s="29"/>
       <c r="O10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1264,7 +1281,7 @@
       <c r="Q10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R10" s="7"/>
+      <c r="R10" s="29"/>
       <c r="S10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1286,14 +1303,14 @@
       <c r="F11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="8"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="15"/>
       <c r="I11" s="8"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
+      <c r="N11" s="30"/>
       <c r="O11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1303,7 +1320,7 @@
       <c r="Q11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="8"/>
+      <c r="R11" s="30"/>
       <c r="S11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1354,7 +1371,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="15"/>
-      <c r="G13" s="8"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="12" t="s">
         <v>21</v>
       </c>
@@ -1362,18 +1379,18 @@
       <c r="J13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="8"/>
+      <c r="K13" s="30"/>
       <c r="L13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="M13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="8"/>
+      <c r="N13" s="30"/>
       <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
+      <c r="P13" s="30"/>
       <c r="Q13" s="15"/>
-      <c r="R13" s="4" t="s">
+      <c r="R13" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S13" s="4" t="s">
@@ -1399,7 +1416,7 @@
       <c r="F14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="7"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="14"/>
       <c r="I14" s="6" t="s">
         <v>21</v>
@@ -1407,31 +1424,29 @@
       <c r="J14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="Q14" s="14"/>
-      <c r="R14" s="6" t="s">
+      <c r="R14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="S14" s="7"/>
       <c r="T14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="U14" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="U14" s="5"/>
     </row>
     <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
@@ -1450,7 +1465,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15"/>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="15"/>
@@ -1458,7 +1473,7 @@
         <v>21</v>
       </c>
       <c r="J15" s="15"/>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -1467,17 +1482,17 @@
       <c r="M15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="P15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="Q15" s="15"/>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S15" s="4" t="s">
@@ -1532,7 +1547,7 @@
       <c r="F17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -1544,7 +1559,7 @@
       <c r="J17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L17" s="4" t="s">
@@ -1553,13 +1568,13 @@
       <c r="M17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
+      <c r="P17" s="30"/>
       <c r="Q17" s="15"/>
-      <c r="R17" s="4" t="s">
+      <c r="R17" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S17" s="4" t="s">
@@ -1587,7 +1602,7 @@
       <c r="F18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="29"/>
       <c r="H18" s="13" t="s">
         <v>21</v>
       </c>
@@ -1595,20 +1610,20 @@
       <c r="J18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="7"/>
+      <c r="K18" s="29"/>
       <c r="L18" s="7"/>
       <c r="M18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="23" t="s">
         <v>21</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="P18" s="7"/>
+      <c r="P18" s="29"/>
       <c r="Q18" s="14"/>
-      <c r="R18" s="6" t="s">
+      <c r="R18" s="23" t="s">
         <v>21</v>
       </c>
       <c r="S18" s="6" t="s">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="8"/>
+      <c r="G19" s="30"/>
       <c r="H19" s="12" t="s">
         <v>21</v>
       </c>
@@ -1638,20 +1653,20 @@
       <c r="J19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
+      <c r="P19" s="30"/>
       <c r="Q19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S19" s="4" t="s">
@@ -1700,7 +1715,7 @@
       <c r="F21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="12" t="s">
@@ -1710,18 +1725,18 @@
         <v>21</v>
       </c>
       <c r="J21" s="15"/>
-      <c r="K21" s="8"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
+      <c r="N21" s="30"/>
       <c r="O21" s="8"/>
-      <c r="P21" s="4" t="s">
+      <c r="P21" s="22" t="s">
         <v>21</v>
       </c>
       <c r="Q21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="R21" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S21" s="8"/>
@@ -1743,7 +1758,7 @@
       <c r="F22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="23" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="14"/>
@@ -1751,18 +1766,18 @@
         <v>21</v>
       </c>
       <c r="J22" s="14"/>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
+      <c r="N22" s="29"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
+      <c r="P22" s="29"/>
       <c r="Q22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="7"/>
+      <c r="R22" s="29"/>
       <c r="S22" s="6" t="s">
         <v>21</v>
       </c>
@@ -1780,7 +1795,7 @@
       <c r="D23" s="20"/>
       <c r="E23" s="8"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="8"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="12" t="s">
         <v>21</v>
       </c>
@@ -1788,20 +1803,20 @@
         <v>21</v>
       </c>
       <c r="J23" s="15"/>
-      <c r="K23" s="8"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="8"/>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P23" s="8"/>
+      <c r="P23" s="30"/>
       <c r="Q23" s="15"/>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S23" s="8"/>
@@ -1821,24 +1836,24 @@
       <c r="F24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="7"/>
+      <c r="G24" s="29"/>
       <c r="H24" s="14"/>
       <c r="I24" s="7"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="23" t="s">
         <v>21</v>
       </c>
       <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
+      <c r="P24" s="29"/>
       <c r="Q24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R24" s="7"/>
+      <c r="R24" s="29"/>
       <c r="S24" s="6" t="s">
         <v>21</v>
       </c>
@@ -1860,26 +1875,26 @@
       <c r="D25" s="20"/>
       <c r="E25" s="8"/>
       <c r="F25" s="15"/>
-      <c r="G25" s="8"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="15"/>
       <c r="I25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="15"/>
-      <c r="K25" s="8"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N25" s="8"/>
+      <c r="N25" s="30"/>
       <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
+      <c r="P25" s="30"/>
       <c r="Q25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R25" s="8"/>
+      <c r="R25" s="30"/>
       <c r="S25" s="4" t="s">
         <v>21</v>
       </c>
@@ -1926,7 +1941,7 @@
       <c r="F27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="12" t="s">
@@ -1936,24 +1951,24 @@
         <v>21</v>
       </c>
       <c r="J27" s="15"/>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
-      <c r="N27" s="4" t="s">
+      <c r="N27" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P27" s="4" t="s">
+      <c r="P27" s="22" t="s">
         <v>21</v>
       </c>
       <c r="Q27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="R27" s="22" t="s">
         <v>21</v>
       </c>
       <c r="S27" s="4" t="s">
@@ -1981,7 +1996,7 @@
       <c r="F28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="23" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="13" t="s">
@@ -1991,22 +2006,22 @@
         <v>21</v>
       </c>
       <c r="J28" s="14"/>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="23" t="s">
         <v>21</v>
       </c>
       <c r="L28" s="7"/>
       <c r="M28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="23" t="s">
         <v>21</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="P28" s="7"/>
+      <c r="P28" s="29"/>
       <c r="Q28" s="14"/>
-      <c r="R28" s="7"/>
+      <c r="R28" s="29"/>
       <c r="S28" s="6" t="s">
         <v>21</v>
       </c>
@@ -2030,7 +2045,7 @@
       <c r="F29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="12" t="s">
@@ -2042,26 +2057,26 @@
       <c r="J29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="22" t="s">
         <v>21</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="P29" s="4" t="s">
+      <c r="P29" s="22" t="s">
         <v>21</v>
       </c>
       <c r="Q29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R29" s="8"/>
+      <c r="R29" s="30"/>
       <c r="S29" s="4" t="s">
         <v>21</v>
       </c>
@@ -2081,7 +2096,7 @@
       <c r="D30" s="19"/>
       <c r="E30" s="7"/>
       <c r="F30" s="14"/>
-      <c r="G30" s="7"/>
+      <c r="G30" s="29"/>
       <c r="H30" s="14"/>
       <c r="I30" s="6" t="s">
         <v>21</v>
@@ -2089,16 +2104,16 @@
       <c r="J30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="7"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
-      <c r="N30" s="6" t="s">
+      <c r="N30" s="23" t="s">
         <v>21</v>
       </c>
       <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
+      <c r="P30" s="29"/>
       <c r="Q30" s="14"/>
-      <c r="R30" s="6" t="s">
+      <c r="R30" s="23" t="s">
         <v>21</v>
       </c>
       <c r="S30" s="7"/>
@@ -2122,11 +2137,11 @@
       <c r="F31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="8"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="15"/>
       <c r="I31" s="8"/>
       <c r="J31" s="15"/>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="22" t="s">
         <v>21</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -2135,11 +2150,11 @@
       <c r="M31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N31" s="8"/>
+      <c r="N31" s="30"/>
       <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
+      <c r="P31" s="30"/>
       <c r="Q31" s="15"/>
-      <c r="R31" s="8"/>
+      <c r="R31" s="30"/>
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
       <c r="U31" s="5" t="s">
